--- a/ClassMaterial/1차 프로젝트/6. API설계/6. API설계(김현규).xlsx
+++ b/ClassMaterial/1차 프로젝트/6. API설계/6. API설계(김현규).xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DW-203\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\KHK\JavaClass\ClassMaterial\1차 프로젝트\6. API설계\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -40,7 +40,7 @@
     <author>DW-203</author>
   </authors>
   <commentList>
-    <comment ref="D6" authorId="0" shapeId="0">
+    <comment ref="D17" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -137,7 +137,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="238">
   <si>
     <t>API 설계</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -187,57 +187,13 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>dia-001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>일기 작성 화면</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>/diaires/save</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>웹캠 PTZ 제어</t>
   </si>
   <si>
     <t>POST</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">일기작성 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>title, content, image, tag</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>title="제목",content="내용", image="경로"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>일기목록 HTML</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>일기목록페이지 제공</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>O</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>인증/회원 API</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>웹캠 PTZ 제어</t>
-  </si>
-  <si>
-    <t>POST</t>
-  </si>
-  <si>
-    <t>O</t>
   </si>
   <si>
     <t>조회</t>
@@ -279,9 +235,6 @@
     <t>/dashboards/main?pet_id=1</t>
   </si>
   <si>
-    <t>대시보드 HTML</t>
-  </si>
-  <si>
     <t>대시보드 페이지 렌더링</t>
   </si>
   <si>
@@ -397,10 +350,6 @@
     <t>화면</t>
   </si>
   <si>
-    <t>권한 체크 후, 선택한 반려동물의 대시보드 UI를 표시</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>사료 급여(즉시/예약) 명령 전송 및 애니메이션 UI 출력을 위한 결과 반환</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -689,6 +638,276 @@
   </si>
   <si>
     <t>저장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>회원가입 화면</t>
+  </si>
+  <si>
+    <t>/auth/signup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">회원가입 입력 폼 화면 렌더링 </t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>회원가입 페이지</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>API</t>
+  </si>
+  <si>
+    <t>회원가입 처리</t>
+  </si>
+  <si>
+    <t xml:space="preserve">입력받은 정보 검증 후 DB 계정 생성 </t>
+  </si>
+  <si>
+    <t>{"user_id": "test", ...}</t>
+  </si>
+  <si>
+    <t>{"status": "success"}</t>
+  </si>
+  <si>
+    <t>로그인 화면</t>
+  </si>
+  <si>
+    <t>/auth/login</t>
+  </si>
+  <si>
+    <t xml:space="preserve">아이디/비번 입력 로그인 화면 렌더링 </t>
+  </si>
+  <si>
+    <t>로그인 페이지</t>
+  </si>
+  <si>
+    <t>로그인 처리</t>
+  </si>
+  <si>
+    <t xml:space="preserve">계정 검증 및 세션/토큰 발급 </t>
+  </si>
+  <si>
+    <t>{"user_id": "test", "user_password": "pw"}</t>
+  </si>
+  <si>
+    <t>인증 결과 (JSON)</t>
+  </si>
+  <si>
+    <t>랜딩 페이지</t>
+  </si>
+  <si>
+    <t>/landing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">서비스 소개 및 3D 인터랙션 화면 (비로그인) </t>
+  </si>
+  <si>
+    <t>메인 화면 조회</t>
+  </si>
+  <si>
+    <t>/main</t>
+  </si>
+  <si>
+    <t xml:space="preserve">로그인 상태에 따른 반려동물/알림/이벤트 요약 화면 </t>
+  </si>
+  <si>
+    <t>세션 정보</t>
+  </si>
+  <si>
+    <t>메인 대시보드 요약</t>
+  </si>
+  <si>
+    <t>user_id, user_password, user_name, user_phone, user_email</t>
+  </si>
+  <si>
+    <t>user_id, user_password</t>
+  </si>
+  <si>
+    <t>갤러리 화면</t>
+  </si>
+  <si>
+    <t>/media</t>
+  </si>
+  <si>
+    <t xml:space="preserve">이미지/동영상을 표시하는 갤러리 화면 제공 </t>
+  </si>
+  <si>
+    <t>미디어 갤러리 뷰</t>
+  </si>
+  <si>
+    <t>하이라이트 조회</t>
+  </si>
+  <si>
+    <t xml:space="preserve">펫ID 및 조건(이벤트 유형)에 따른 목록 조회 </t>
+  </si>
+  <si>
+    <t>/api/media/highlights?pet_id=1</t>
+  </si>
+  <si>
+    <t>미디어 목록 (JSON)</t>
+  </si>
+  <si>
+    <t>{"data": [{"media_id": 1}]}</t>
+  </si>
+  <si>
+    <t>하이라이트 소통 설정</t>
+  </si>
+  <si>
+    <t xml:space="preserve">문자/SNS 전송 방식(자동/수동) 설정 업데이트 </t>
+  </si>
+  <si>
+    <t>{"share_channel": "SNS", "is_auto": true}</t>
+  </si>
+  <si>
+    <t>설정 결과 (JSON)</t>
+  </si>
+  <si>
+    <t>pet_id (Long), event_code (String)</t>
+  </si>
+  <si>
+    <t>media_id (Long), share_channel (String), is_auto (Boolean)</t>
+  </si>
+  <si>
+    <t>세션 (ROLE_ADMIN)</t>
+  </si>
+  <si>
+    <t>시뮬레이션 UI 화면</t>
+  </si>
+  <si>
+    <t>/admin/sim</t>
+  </si>
+  <si>
+    <t xml:space="preserve">상태 데이터 입력 및 테스트 UI 제공 </t>
+  </si>
+  <si>
+    <t>시뮬레이터 뷰</t>
+  </si>
+  <si>
+    <t>시뮬레이션 데이터 관리</t>
+  </si>
+  <si>
+    <t>POST/GET</t>
+  </si>
+  <si>
+    <t xml:space="preserve">원시 데이터(Raw) 가상 생성 전송 및 DB 목록 조회 </t>
+  </si>
+  <si>
+    <t>{"heart_rate": 120}</t>
+  </si>
+  <si>
+    <t>생성/조회 (JSON)</t>
+  </si>
+  <si>
+    <t>pet_id, heart_rate, temperature 등</t>
+  </si>
+  <si>
+    <t>Adm-011</t>
+  </si>
+  <si>
+    <t>Adm-012</t>
+  </si>
+  <si>
+    <t>Auth-001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Auth-002</t>
+  </si>
+  <si>
+    <t>Auth-003</t>
+  </si>
+  <si>
+    <t>Auth-004</t>
+  </si>
+  <si>
+    <t>Main-001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Main-002</t>
+  </si>
+  <si>
+    <t>Media-001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Media-002</t>
+  </si>
+  <si>
+    <t>Media-003</t>
+  </si>
+  <si>
+    <t>Media-004</t>
+  </si>
+  <si>
+    <t>Media-005</t>
+  </si>
+  <si>
+    <t>Media-006</t>
+  </si>
+  <si>
+    <t>/auth/signup</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/auth/login</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/media/highlights</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/media/{media_id}/share</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/media/highlights</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/media/{media_id}/share</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/admin/sim/state</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>제어</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>제어</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조회</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조회</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조회</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>대시보드 HTML + Model</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>권한 체크 후, 선택한 반려동물의 관제 대시보드을 서버에서 렌더링하고 초기 모델 데이터 UI를 표시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pet_id</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -696,7 +915,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -713,29 +932,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0" tint="-0.34998626667073579"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0" tint="-0.34998626667073579"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF1F1F1F"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FF1F1F1F"/>
       <name val="Arial"/>
@@ -888,18 +1084,21 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -918,27 +1117,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1274,7 +1452,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K45"/>
+  <dimension ref="A1:K35"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="10.375" customWidth="1"/>
@@ -1288,876 +1466,1187 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="6"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="7"/>
     </row>
     <row r="2" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="7"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="9"/>
+      <c r="A2" s="8"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="10"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="G3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="H3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="10" t="s">
+      <c r="I3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="10" t="s">
+      <c r="J3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="10" t="s">
+      <c r="K3" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="33" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="33" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="33" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="1" t="s">
+      <c r="E20" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="F20" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="K20" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="1" t="s">
+    </row>
+    <row r="21" spans="1:11" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="33" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="33" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="B25" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K4" s="12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="13" t="s">
-        <v>163</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="E5" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="G5" s="13" t="s">
+      <c r="F25" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="33" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="H5" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="I5" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="J5" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="K5" s="13" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="A6" s="13" t="s">
+      <c r="B29" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="J35" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="B6" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="E6" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="G6" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="H6" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="I6" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="J6" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="K6" s="13" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="A7" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="E7" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="F7" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="G7" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="H7" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="I7" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="J7" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="K7" s="13" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="33" x14ac:dyDescent="0.3">
-      <c r="A8" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="E8" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="F8" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="G8" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="H8" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="I8" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="J8" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="K8" s="13" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="A9" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="E9" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="F9" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="G9" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="H9" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="I9" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="J9" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="K9" s="13" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="A10" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="F10" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="G10" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="H10" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="I10" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="J10" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="K10" s="13" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="A11" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="E11" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="G11" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="H11" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="I11" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="J11" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="K11" s="13" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="33" x14ac:dyDescent="0.3">
-      <c r="A12" s="13" t="s">
-        <v>166</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="E12" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="F12" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="G12" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="H12" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="I12" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="J12" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="K12" s="13" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="33" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F13" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F14" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="F16" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="F17" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" ht="33" x14ac:dyDescent="0.3">
-      <c r="A18" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F18" s="13" t="s">
-        <v>142</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A19" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F19" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A20" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F20" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A21" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F21" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A22" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="F22" s="13" t="s">
-        <v>146</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A28" s="14"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A29" s="14"/>
-      <c r="B29" s="15"/>
-      <c r="C29" s="15"/>
-      <c r="D29" s="15"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A30" s="14"/>
-      <c r="B30" s="15"/>
-      <c r="C30" s="16"/>
-      <c r="D30" s="15"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A31" s="14"/>
-      <c r="B31" s="15"/>
-      <c r="C31" s="16"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A32" s="14"/>
-      <c r="B32" s="15"/>
-      <c r="C32" s="16"/>
-      <c r="D32" s="15"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="14"/>
-      <c r="B33" s="15"/>
-      <c r="C33" s="16"/>
-      <c r="D33" s="15"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="14"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="14"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="14"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="14"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="14"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="14"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="14"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="14"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="14"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="14"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="14"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="14"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
+      <c r="K35" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
